--- a/estimation/notsensor/DenseModel/Dense_1st_torch_optimized/IWALQQ_1st_correction/angle/4_fold/55.xlsx
+++ b/estimation/notsensor/DenseModel/Dense_1st_torch_optimized/IWALQQ_1st_correction/angle/4_fold/55.xlsx
@@ -426,13 +426,13 @@
         <v>-7.517204896889749</v>
       </c>
       <c r="E2">
-        <v>-17.09879084535564</v>
+        <v>-19.63996214865589</v>
       </c>
       <c r="F2">
-        <v>5.973909715397395</v>
+        <v>2.787157122540418</v>
       </c>
       <c r="G2">
-        <v>-18.51177976747997</v>
+        <v>-18.98693674272472</v>
       </c>
     </row>
     <row r="3" spans="1:7">
@@ -449,13 +449,13 @@
         <v>-7.099841063655729</v>
       </c>
       <c r="E3">
-        <v>-16.33379573123988</v>
+        <v>-18.39196905383003</v>
       </c>
       <c r="F3">
-        <v>6.754170509646721</v>
+        <v>3.445351353048016</v>
       </c>
       <c r="G3">
-        <v>-17.17488869896449</v>
+        <v>-19.56489931125921</v>
       </c>
     </row>
     <row r="4" spans="1:7">
@@ -472,13 +472,13 @@
         <v>-6.630094926413733</v>
       </c>
       <c r="E4">
-        <v>-16.95569559518726</v>
+        <v>-19.88664624174972</v>
       </c>
       <c r="F4">
-        <v>6.203529845983806</v>
+        <v>3.177520290905268</v>
       </c>
       <c r="G4">
-        <v>-17.37296948206505</v>
+        <v>-18.22148681489434</v>
       </c>
     </row>
     <row r="5" spans="1:7">
@@ -495,13 +495,13 @@
         <v>-6.144228989511697</v>
       </c>
       <c r="E5">
-        <v>-16.68759634851115</v>
+        <v>-23.90495142466395</v>
       </c>
       <c r="F5">
-        <v>6.219565382167199</v>
+        <v>4.273266467245593</v>
       </c>
       <c r="G5">
-        <v>-16.5900650961492</v>
+        <v>-17.73136418811696</v>
       </c>
     </row>
     <row r="6" spans="1:7">
@@ -518,13 +518,13 @@
         <v>-5.653495345618386</v>
       </c>
       <c r="E6">
-        <v>-16.95333626022926</v>
+        <v>-21.47962301495392</v>
       </c>
       <c r="F6">
-        <v>6.199502323671395</v>
+        <v>3.496438427513467</v>
       </c>
       <c r="G6">
-        <v>-16.39797254239463</v>
+        <v>-18.78755659588662</v>
       </c>
     </row>
     <row r="7" spans="1:7">
@@ -541,13 +541,13 @@
         <v>-5.179578767985097</v>
       </c>
       <c r="E7">
-        <v>-17.0631698688113</v>
+        <v>-22.32290638771428</v>
       </c>
       <c r="F7">
-        <v>6.300500190890322</v>
+        <v>3.253342416018313</v>
       </c>
       <c r="G7">
-        <v>-16.4433239461785</v>
+        <v>-19.44222756203781</v>
       </c>
     </row>
     <row r="8" spans="1:7">
@@ -564,13 +564,13 @@
         <v>-4.734684500533352</v>
       </c>
       <c r="E8">
-        <v>-17.91392975215832</v>
+        <v>-22.0332787756057</v>
       </c>
       <c r="F8">
-        <v>5.893896051226185</v>
+        <v>3.709290745132411</v>
       </c>
       <c r="G8">
-        <v>-15.42282630714326</v>
+        <v>-16.85910885791587</v>
       </c>
     </row>
     <row r="9" spans="1:7">
@@ -587,13 +587,13 @@
         <v>-4.332660321549496</v>
       </c>
       <c r="E9">
-        <v>-17.25954261567992</v>
+        <v>-22.56871648532463</v>
       </c>
       <c r="F9">
-        <v>6.84986019854851</v>
+        <v>3.679848910902111</v>
       </c>
       <c r="G9">
-        <v>-13.96733056352931</v>
+        <v>-16.65754341751918</v>
       </c>
     </row>
     <row r="10" spans="1:7">
@@ -610,13 +610,13 @@
         <v>-3.981654567109002</v>
       </c>
       <c r="E10">
-        <v>-18.38951462091787</v>
+        <v>-25.57189176383543</v>
       </c>
       <c r="F10">
-        <v>6.487787433724068</v>
+        <v>4.249505576663692</v>
       </c>
       <c r="G10">
-        <v>-14.23176420900496</v>
+        <v>-15.89421972125932</v>
       </c>
     </row>
     <row r="11" spans="1:7">
@@ -633,13 +633,13 @@
         <v>-3.686970009354059</v>
       </c>
       <c r="E11">
-        <v>-20.45826193031593</v>
+        <v>-23.47711931431529</v>
       </c>
       <c r="F11">
-        <v>6.491134038031378</v>
+        <v>3.006465735696782</v>
       </c>
       <c r="G11">
-        <v>-13.40773955450615</v>
+        <v>-16.87061774253563</v>
       </c>
     </row>
     <row r="12" spans="1:7">
@@ -656,13 +656,13 @@
         <v>-3.449087732270111</v>
       </c>
       <c r="E12">
-        <v>-22.70423107000417</v>
+        <v>-25.24943724364525</v>
       </c>
       <c r="F12">
-        <v>6.387992355974005</v>
+        <v>3.71136166363941</v>
       </c>
       <c r="G12">
-        <v>-12.12154992152721</v>
+        <v>-15.20433960716451</v>
       </c>
     </row>
     <row r="13" spans="1:7">
@@ -679,13 +679,13 @@
         <v>-3.264112397471738</v>
       </c>
       <c r="E13">
-        <v>-22.77536886819066</v>
+        <v>-24.32260805391739</v>
       </c>
       <c r="F13">
-        <v>6.256775645900952</v>
+        <v>3.223673609119646</v>
       </c>
       <c r="G13">
-        <v>-11.32455104840277</v>
+        <v>-13.48035298761666</v>
       </c>
     </row>
     <row r="14" spans="1:7">
@@ -702,13 +702,13 @@
         <v>-3.131412002328868</v>
       </c>
       <c r="E14">
-        <v>-20.65406408945958</v>
+        <v>-25.7666433170093</v>
       </c>
       <c r="F14">
-        <v>5.907696652156824</v>
+        <v>4.373321652360134</v>
       </c>
       <c r="G14">
-        <v>-10.81280189032709</v>
+        <v>-13.89294198955514</v>
       </c>
     </row>
     <row r="15" spans="1:7">
@@ -725,13 +725,13 @@
         <v>-3.045779935440476</v>
       </c>
       <c r="E15">
-        <v>-24.04394840585539</v>
+        <v>-27.70449508521564</v>
       </c>
       <c r="F15">
-        <v>6.110646665842704</v>
+        <v>4.154112443292107</v>
       </c>
       <c r="G15">
-        <v>-9.801670498233289</v>
+        <v>-12.82251072082827</v>
       </c>
     </row>
     <row r="16" spans="1:7">
@@ -748,13 +748,13 @@
         <v>-3.000025354690781</v>
       </c>
       <c r="E16">
-        <v>-24.13401069691994</v>
+        <v>-28.52376848878734</v>
       </c>
       <c r="F16">
-        <v>6.51011359196432</v>
+        <v>4.226319573059333</v>
       </c>
       <c r="G16">
-        <v>-8.909736041729433</v>
+        <v>-11.28098626975802</v>
       </c>
     </row>
     <row r="17" spans="1:7">
@@ -771,13 +771,13 @@
         <v>-2.987202070455253</v>
       </c>
       <c r="E17">
-        <v>-25.74352092872613</v>
+        <v>-31.25401037461884</v>
       </c>
       <c r="F17">
-        <v>6.103847426200525</v>
+        <v>3.674893617098564</v>
       </c>
       <c r="G17">
-        <v>-8.961566217482421</v>
+        <v>-13.00119292206939</v>
       </c>
     </row>
     <row r="18" spans="1:7">
@@ -794,13 +794,13 @@
         <v>-2.999983406786472</v>
       </c>
       <c r="E18">
-        <v>-25.52904787124886</v>
+        <v>-29.0248667801061</v>
       </c>
       <c r="F18">
-        <v>6.437966104650094</v>
+        <v>2.762783240080446</v>
       </c>
       <c r="G18">
-        <v>-8.347403572093357</v>
+        <v>-10.3139512142016</v>
       </c>
     </row>
     <row r="19" spans="1:7">
@@ -817,13 +817,13 @@
         <v>-3.030825887481749</v>
       </c>
       <c r="E19">
-        <v>-26.37810957684301</v>
+        <v>-31.95473285714372</v>
       </c>
       <c r="F19">
-        <v>5.890796300404909</v>
+        <v>3.402034364820824</v>
       </c>
       <c r="G19">
-        <v>-7.22359503164822</v>
+        <v>-10.3585955147394</v>
       </c>
     </row>
     <row r="20" spans="1:7">
@@ -840,13 +840,13 @@
         <v>-3.073105296199138</v>
       </c>
       <c r="E20">
-        <v>-27.85157086403676</v>
+        <v>-30.06815926436323</v>
       </c>
       <c r="F20">
-        <v>6.165118449515993</v>
+        <v>3.654727841044813</v>
       </c>
       <c r="G20">
-        <v>-7.008314085133052</v>
+        <v>-10.03039789069906</v>
       </c>
     </row>
     <row r="21" spans="1:7">
@@ -863,13 +863,13 @@
         <v>-3.122108054090482</v>
       </c>
       <c r="E21">
-        <v>-27.55279120595869</v>
+        <v>-32.38131510866627</v>
       </c>
       <c r="F21">
-        <v>5.993899877561752</v>
+        <v>3.532397856468993</v>
       </c>
       <c r="G21">
-        <v>-4.993342175250528</v>
+        <v>-8.621825255995956</v>
       </c>
     </row>
     <row r="22" spans="1:7">
@@ -886,13 +886,13 @@
         <v>-3.177070695061752</v>
       </c>
       <c r="E22">
-        <v>-28.40135477941199</v>
+        <v>-31.24611498018646</v>
       </c>
       <c r="F22">
-        <v>6.180375320340755</v>
+        <v>3.515371592871852</v>
       </c>
       <c r="G22">
-        <v>-3.64777227571032</v>
+        <v>-8.659434617510311</v>
       </c>
     </row>
     <row r="23" spans="1:7">
@@ -909,13 +909,13 @@
         <v>-3.237595166098261</v>
       </c>
       <c r="E23">
-        <v>-29.7275455634023</v>
+        <v>-34.48697627393786</v>
       </c>
       <c r="F23">
-        <v>5.675626210792932</v>
+        <v>3.893622373072968</v>
       </c>
       <c r="G23">
-        <v>-4.198837030511263</v>
+        <v>-8.395240501208502</v>
       </c>
     </row>
     <row r="24" spans="1:7">
@@ -932,13 +932,13 @@
         <v>-3.302757739526853</v>
       </c>
       <c r="E24">
-        <v>-30.13931291220876</v>
+        <v>-32.61844865007793</v>
       </c>
       <c r="F24">
-        <v>5.298054691862111</v>
+        <v>3.180742640102158</v>
       </c>
       <c r="G24">
-        <v>-3.214099784641631</v>
+        <v>-7.418739121453076</v>
       </c>
     </row>
     <row r="25" spans="1:7">
@@ -955,13 +955,13 @@
         <v>-3.374964188884269</v>
       </c>
       <c r="E25">
-        <v>-30.94378273424937</v>
+        <v>-34.09059894404647</v>
       </c>
       <c r="F25">
-        <v>5.528902462939472</v>
+        <v>2.656275072898096</v>
       </c>
       <c r="G25">
-        <v>-3.012278408963305</v>
+        <v>-7.626742318549395</v>
       </c>
     </row>
     <row r="26" spans="1:7">
@@ -978,13 +978,13 @@
         <v>-3.455653600483713</v>
       </c>
       <c r="E26">
-        <v>-30.77292567417697</v>
+        <v>-34.05325941161622</v>
       </c>
       <c r="F26">
-        <v>6.428431595843872</v>
+        <v>2.640555973062573</v>
       </c>
       <c r="G26">
-        <v>-3.191022953414056</v>
+        <v>-6.959784818268865</v>
       </c>
     </row>
     <row r="27" spans="1:7">
@@ -1001,13 +1001,13 @@
         <v>-3.545414539422058</v>
       </c>
       <c r="E27">
-        <v>-30.35082661192202</v>
+        <v>-34.05054006297461</v>
       </c>
       <c r="F27">
-        <v>5.444569691130066</v>
+        <v>3.768363281360849</v>
       </c>
       <c r="G27">
-        <v>-1.0538025718913</v>
+        <v>-4.800849312465703</v>
       </c>
     </row>
     <row r="28" spans="1:7">
@@ -1024,13 +1024,13 @@
         <v>-3.643587982425316</v>
       </c>
       <c r="E28">
-        <v>-32.17433441143469</v>
+        <v>-33.45103123875816</v>
       </c>
       <c r="F28">
-        <v>5.575007735844487</v>
+        <v>4.355349393188995</v>
       </c>
       <c r="G28">
-        <v>-1.215488045454498</v>
+        <v>-4.812773271612725</v>
       </c>
     </row>
     <row r="29" spans="1:7">
@@ -1047,13 +1047,13 @@
         <v>-3.749397717367636</v>
       </c>
       <c r="E29">
-        <v>-31.56428556396538</v>
+        <v>-34.02392848546854</v>
       </c>
       <c r="F29">
-        <v>5.357316095858388</v>
+        <v>2.78449474970782</v>
       </c>
       <c r="G29">
-        <v>-1.230059950399992</v>
+        <v>-4.467300016061911</v>
       </c>
     </row>
     <row r="30" spans="1:7">
@@ -1070,13 +1070,13 @@
         <v>-3.86178161211898</v>
       </c>
       <c r="E30">
-        <v>-29.77711197565326</v>
+        <v>-32.42177928816181</v>
       </c>
       <c r="F30">
-        <v>5.648899764909008</v>
+        <v>2.948156954213724</v>
       </c>
       <c r="G30">
-        <v>-0.783295385309118</v>
+        <v>-3.269785395726967</v>
       </c>
     </row>
     <row r="31" spans="1:7">
@@ -1093,13 +1093,13 @@
         <v>-3.978083302355463</v>
       </c>
       <c r="E31">
-        <v>-30.52730350823794</v>
+        <v>-33.22596834481395</v>
       </c>
       <c r="F31">
-        <v>5.417092744379206</v>
+        <v>2.730947424056055</v>
       </c>
       <c r="G31">
-        <v>-1.096461733385641</v>
+        <v>-5.377231972819322</v>
       </c>
     </row>
     <row r="32" spans="1:7">
@@ -1116,13 +1116,13 @@
         <v>-4.09388568854791</v>
       </c>
       <c r="E32">
-        <v>-30.40184666432944</v>
+        <v>-32.20299738766624</v>
       </c>
       <c r="F32">
-        <v>5.28169112218721</v>
+        <v>2.670662157949918</v>
       </c>
       <c r="G32">
-        <v>-2.990005477017794</v>
+        <v>-4.494012440777349</v>
       </c>
     </row>
     <row r="33" spans="1:7">
@@ -1139,13 +1139,13 @@
         <v>-4.207229015124089</v>
       </c>
       <c r="E33">
-        <v>-30.99907087340902</v>
+        <v>-33.17143193233957</v>
       </c>
       <c r="F33">
-        <v>5.638036554788695</v>
+        <v>2.274208832439686</v>
       </c>
       <c r="G33">
-        <v>-1.701450083294498</v>
+        <v>-4.328727467163441</v>
       </c>
     </row>
     <row r="34" spans="1:7">
@@ -1162,13 +1162,13 @@
         <v>-4.314405946445151</v>
       </c>
       <c r="E34">
-        <v>-28.34413298185107</v>
+        <v>-32.85198431889049</v>
       </c>
       <c r="F34">
-        <v>5.649627071488666</v>
+        <v>2.538139940850053</v>
       </c>
       <c r="G34">
-        <v>-1.13020909712453</v>
+        <v>-4.035858755653644</v>
       </c>
     </row>
     <row r="35" spans="1:7">
@@ -1185,13 +1185,13 @@
         <v>-4.41152810851494</v>
       </c>
       <c r="E35">
-        <v>-29.37467781177661</v>
+        <v>-31.61319761172223</v>
       </c>
       <c r="F35">
-        <v>5.607484708238644</v>
+        <v>2.332732989447471</v>
       </c>
       <c r="G35">
-        <v>-0.3220901641351282</v>
+        <v>-4.65627540933501</v>
       </c>
     </row>
     <row r="36" spans="1:7">
@@ -1208,13 +1208,13 @@
         <v>-4.494255729920759</v>
       </c>
       <c r="E36">
-        <v>-27.96048066392123</v>
+        <v>-34.45327537037277</v>
       </c>
       <c r="F36">
-        <v>5.536705683873843</v>
+        <v>2.810044913879768</v>
       </c>
       <c r="G36">
-        <v>-2.014642681143496</v>
+        <v>-6.355370682132911</v>
       </c>
     </row>
     <row r="37" spans="1:7">
@@ -1231,13 +1231,13 @@
         <v>-4.56044680110839</v>
       </c>
       <c r="E37">
-        <v>-28.83981068978265</v>
+        <v>-31.35213108518003</v>
       </c>
       <c r="F37">
-        <v>5.564091510210395</v>
+        <v>2.300728186472909</v>
       </c>
       <c r="G37">
-        <v>-4.206994147308042</v>
+        <v>-7.205912528664372</v>
       </c>
     </row>
     <row r="38" spans="1:7">
@@ -1254,13 +1254,13 @@
         <v>-4.608956601729252</v>
       </c>
       <c r="E38">
-        <v>-27.94763791163548</v>
+        <v>-32.14345701141339</v>
       </c>
       <c r="F38">
-        <v>6.435068475475101</v>
+        <v>3.331030024522462</v>
       </c>
       <c r="G38">
-        <v>-3.652638327282976</v>
+        <v>-7.131665047217258</v>
       </c>
     </row>
     <row r="39" spans="1:7">
@@ -1277,13 +1277,13 @@
         <v>-4.639095642611261</v>
       </c>
       <c r="E39">
-        <v>-29.38823606295557</v>
+        <v>-29.96737807532253</v>
       </c>
       <c r="F39">
-        <v>6.249618551540765</v>
+        <v>3.826440119971123</v>
       </c>
       <c r="G39">
-        <v>-4.064395539556134</v>
+        <v>-8.172130560052498</v>
       </c>
     </row>
     <row r="40" spans="1:7">
@@ -1300,13 +1300,13 @@
         <v>-4.651983626273227</v>
       </c>
       <c r="E40">
-        <v>-27.41088241598032</v>
+        <v>-31.04214798240698</v>
       </c>
       <c r="F40">
-        <v>6.172809012483584</v>
+        <v>3.865673256902513</v>
       </c>
       <c r="G40">
-        <v>-4.172515071161397</v>
+        <v>-8.109091731452446</v>
       </c>
     </row>
     <row r="41" spans="1:7">
@@ -1323,13 +1323,13 @@
         <v>-4.652785716224222</v>
       </c>
       <c r="E41">
-        <v>-25.9160693738404</v>
+        <v>-29.46873874538993</v>
       </c>
       <c r="F41">
-        <v>6.817220866143403</v>
+        <v>3.563329095289527</v>
       </c>
       <c r="G41">
-        <v>-4.869499029932406</v>
+        <v>-6.989975337837316</v>
       </c>
     </row>
     <row r="42" spans="1:7">
@@ -1346,13 +1346,13 @@
         <v>-4.647431611600376</v>
       </c>
       <c r="E42">
-        <v>-26.21117191102424</v>
+        <v>-28.80284022798403</v>
       </c>
       <c r="F42">
-        <v>6.617511425737276</v>
+        <v>3.809460244948538</v>
       </c>
       <c r="G42">
-        <v>-3.943692523270401</v>
+        <v>-7.052462921215381</v>
       </c>
     </row>
     <row r="43" spans="1:7">
@@ -1369,13 +1369,13 @@
         <v>-4.643054291397349</v>
       </c>
       <c r="E43">
-        <v>-25.48163021991454</v>
+        <v>-26.64274906937725</v>
       </c>
       <c r="F43">
-        <v>6.938192328178632</v>
+        <v>4.304323617911352</v>
       </c>
       <c r="G43">
-        <v>-4.581726055504426</v>
+        <v>-8.435737337695167</v>
       </c>
     </row>
     <row r="44" spans="1:7">
@@ -1392,13 +1392,13 @@
         <v>-4.646365377347505</v>
       </c>
       <c r="E44">
-        <v>-25.83191674135586</v>
+        <v>-26.50181390131053</v>
       </c>
       <c r="F44">
-        <v>6.941500827585413</v>
+        <v>3.021270317919614</v>
       </c>
       <c r="G44">
-        <v>-4.70603185306243</v>
+        <v>-7.379331650524144</v>
       </c>
     </row>
     <row r="45" spans="1:7">
@@ -1415,13 +1415,13 @@
         <v>-4.666963724003299</v>
       </c>
       <c r="E45">
-        <v>-24.345408920546</v>
+        <v>-27.31507349140004</v>
       </c>
       <c r="F45">
-        <v>7.143851103271665</v>
+        <v>4.634449565479428</v>
       </c>
       <c r="G45">
-        <v>-5.731830305526953</v>
+        <v>-9.747274407220814</v>
       </c>
     </row>
     <row r="46" spans="1:7">
@@ -1438,13 +1438,13 @@
         <v>-4.712103603094795</v>
       </c>
       <c r="E46">
-        <v>-22.70496921126742</v>
+        <v>-24.10680815355586</v>
       </c>
       <c r="F46">
-        <v>7.621187878726047</v>
+        <v>3.799682196125893</v>
       </c>
       <c r="G46">
-        <v>-5.154732338873376</v>
+        <v>-9.917139966131709</v>
       </c>
     </row>
     <row r="47" spans="1:7">
@@ -1461,13 +1461,13 @@
         <v>-4.785639658204197</v>
       </c>
       <c r="E47">
-        <v>-22.74440316292621</v>
+        <v>-25.87006460639648</v>
       </c>
       <c r="F47">
-        <v>7.717916340350945</v>
+        <v>3.977246062385578</v>
       </c>
       <c r="G47">
-        <v>-6.746479167132483</v>
+        <v>-9.45675176912602</v>
       </c>
     </row>
     <row r="48" spans="1:7">
@@ -1484,13 +1484,13 @@
         <v>-4.891007662721562</v>
       </c>
       <c r="E48">
-        <v>-23.25629733627926</v>
+        <v>-26.20250441177356</v>
       </c>
       <c r="F48">
-        <v>7.531720885754089</v>
+        <v>5.147333242922741</v>
       </c>
       <c r="G48">
-        <v>-6.371921163678749</v>
+        <v>-10.36418999749825</v>
       </c>
     </row>
     <row r="49" spans="1:7">
@@ -1507,13 +1507,13 @@
         <v>-5.030014335310579</v>
       </c>
       <c r="E49">
-        <v>-21.53424093996043</v>
+        <v>-22.35685182887577</v>
       </c>
       <c r="F49">
-        <v>7.79150187347643</v>
+        <v>5.30013720751275</v>
       </c>
       <c r="G49">
-        <v>-7.42668952129161</v>
+        <v>-10.46376850938428</v>
       </c>
     </row>
     <row r="50" spans="1:7">
@@ -1530,13 +1530,13 @@
         <v>-5.201013325980188</v>
       </c>
       <c r="E50">
-        <v>-21.86959255412445</v>
+        <v>-22.26713823030981</v>
       </c>
       <c r="F50">
-        <v>8.131717336010604</v>
+        <v>5.672248128524315</v>
       </c>
       <c r="G50">
-        <v>-6.920534845974787</v>
+        <v>-10.34157581851056</v>
       </c>
     </row>
     <row r="51" spans="1:7">
@@ -1553,13 +1553,13 @@
         <v>-5.399721506461971</v>
       </c>
       <c r="E51">
-        <v>-20.9496240025182</v>
+        <v>-22.84355410132415</v>
       </c>
       <c r="F51">
-        <v>7.877627232345495</v>
+        <v>5.172436088697178</v>
       </c>
       <c r="G51">
-        <v>-6.02221513231625</v>
+        <v>-9.832018516436595</v>
       </c>
     </row>
     <row r="52" spans="1:7">
@@ -1576,13 +1576,13 @@
         <v>-5.619554006335621</v>
       </c>
       <c r="E52">
-        <v>-19.23306064517068</v>
+        <v>-23.8513705202052</v>
       </c>
       <c r="F52">
-        <v>8.241871976500077</v>
+        <v>5.143585708792476</v>
       </c>
       <c r="G52">
-        <v>-6.8502576426146</v>
+        <v>-13.16946708852395</v>
       </c>
     </row>
     <row r="53" spans="1:7">
@@ -1599,13 +1599,13 @@
         <v>-5.855138206789687</v>
       </c>
       <c r="E53">
-        <v>-19.40534191031849</v>
+        <v>-19.90541676651152</v>
       </c>
       <c r="F53">
-        <v>8.25177096696353</v>
+        <v>5.744070895816644</v>
       </c>
       <c r="G53">
-        <v>-7.889049732454525</v>
+        <v>-11.73675778802957</v>
       </c>
     </row>
     <row r="54" spans="1:7">
@@ -1622,13 +1622,13 @@
         <v>-6.098582705794715</v>
       </c>
       <c r="E54">
-        <v>-17.28167779662941</v>
+        <v>-20.04474432630551</v>
       </c>
       <c r="F54">
-        <v>7.979582692282058</v>
+        <v>4.725329753240561</v>
       </c>
       <c r="G54">
-        <v>-7.909517992542341</v>
+        <v>-13.07739601156594</v>
       </c>
     </row>
     <row r="55" spans="1:7">
@@ -1645,13 +1645,13 @@
         <v>-6.338674809665179</v>
       </c>
       <c r="E55">
-        <v>-17.65440743525274</v>
+        <v>-18.16303205037226</v>
       </c>
       <c r="F55">
-        <v>9.07558566251725</v>
+        <v>5.392917670095906</v>
       </c>
       <c r="G55">
-        <v>-7.543382884831701</v>
+        <v>-11.47251445340437</v>
       </c>
     </row>
     <row r="56" spans="1:7">
@@ -1668,13 +1668,13 @@
         <v>-6.568531832495252</v>
       </c>
       <c r="E56">
-        <v>-15.28833863640708</v>
+        <v>-18.02534832664304</v>
       </c>
       <c r="F56">
-        <v>8.297185381454611</v>
+        <v>5.786055869260133</v>
       </c>
       <c r="G56">
-        <v>-9.089002300408135</v>
+        <v>-14.81263886167346</v>
       </c>
     </row>
     <row r="57" spans="1:7">
@@ -1691,13 +1691,13 @@
         <v>-6.781070587095319</v>
       </c>
       <c r="E57">
-        <v>-17.89244214299193</v>
+        <v>-16.53201609550363</v>
       </c>
       <c r="F57">
-        <v>8.321734877803978</v>
+        <v>5.132533630904326</v>
       </c>
       <c r="G57">
-        <v>-7.481216861166462</v>
+        <v>-13.62104520564253</v>
       </c>
     </row>
     <row r="58" spans="1:7">
@@ -1714,13 +1714,13 @@
         <v>-6.969935693831251</v>
       </c>
       <c r="E58">
-        <v>-15.69147697799192</v>
+        <v>-15.27756539674283</v>
       </c>
       <c r="F58">
-        <v>8.267720352937033</v>
+        <v>5.84821987263582</v>
       </c>
       <c r="G58">
-        <v>-8.490704361258986</v>
+        <v>-12.66493661787906</v>
       </c>
     </row>
     <row r="59" spans="1:7">
@@ -1737,13 +1737,13 @@
         <v>-7.129527001203527</v>
       </c>
       <c r="E59">
-        <v>-14.65291222059879</v>
+        <v>-17.74191566697696</v>
       </c>
       <c r="F59">
-        <v>8.619204925618892</v>
+        <v>5.181577951354473</v>
       </c>
       <c r="G59">
-        <v>-9.149868960335835</v>
+        <v>-13.24741250666856</v>
       </c>
     </row>
     <row r="60" spans="1:7">
@@ -1760,13 +1760,13 @@
         <v>-7.256457825334612</v>
       </c>
       <c r="E60">
-        <v>-15.38455965212206</v>
+        <v>-16.67270219749993</v>
       </c>
       <c r="F60">
-        <v>8.060911803888914</v>
+        <v>6.416226430531024</v>
       </c>
       <c r="G60">
-        <v>-8.17370882762259</v>
+        <v>-14.62210160693806</v>
       </c>
     </row>
     <row r="61" spans="1:7">
@@ -1783,13 +1783,13 @@
         <v>-7.350568969094041</v>
       </c>
       <c r="E61">
-        <v>-13.97893943403721</v>
+        <v>-13.66908312853638</v>
       </c>
       <c r="F61">
-        <v>8.609547818437054</v>
+        <v>4.979318796082529</v>
       </c>
       <c r="G61">
-        <v>-9.197971668397294</v>
+        <v>-14.53647320851201</v>
       </c>
     </row>
     <row r="62" spans="1:7">
@@ -1806,13 +1806,13 @@
         <v>-7.411618747768091</v>
       </c>
       <c r="E62">
-        <v>-14.25494539633071</v>
+        <v>-14.8551266989373</v>
       </c>
       <c r="F62">
-        <v>8.198720661753445</v>
+        <v>5.316021980828832</v>
       </c>
       <c r="G62">
-        <v>-8.065244767753587</v>
+        <v>-13.77394192725876</v>
       </c>
     </row>
     <row r="63" spans="1:7">
@@ -1829,13 +1829,13 @@
         <v>-7.438579880114164</v>
       </c>
       <c r="E63">
-        <v>-12.75102106448736</v>
+        <v>-17.38691047561965</v>
       </c>
       <c r="F63">
-        <v>7.908311617679995</v>
+        <v>5.711366950754119</v>
       </c>
       <c r="G63">
-        <v>-8.756194560076777</v>
+        <v>-12.87170279444747</v>
       </c>
     </row>
     <row r="64" spans="1:7">
@@ -1852,13 +1852,13 @@
         <v>-7.436511552674245</v>
       </c>
       <c r="E64">
-        <v>-14.08349737040031</v>
+        <v>-15.96890035264982</v>
       </c>
       <c r="F64">
-        <v>7.689069273915855</v>
+        <v>4.772274990692015</v>
       </c>
       <c r="G64">
-        <v>-9.251652453109809</v>
+        <v>-14.65266618576429</v>
       </c>
     </row>
     <row r="65" spans="1:7">
@@ -1875,13 +1875,13 @@
         <v>-7.409651976603903</v>
       </c>
       <c r="E65">
-        <v>-13.68207984893839</v>
+        <v>-14.5692577202551</v>
       </c>
       <c r="F65">
-        <v>7.379723751014407</v>
+        <v>5.163766395459478</v>
       </c>
       <c r="G65">
-        <v>-8.748887279663894</v>
+        <v>-14.58254812164974</v>
       </c>
     </row>
     <row r="66" spans="1:7">
@@ -1898,13 +1898,13 @@
         <v>-7.363042126177944</v>
       </c>
       <c r="E66">
-        <v>-14.72640482526927</v>
+        <v>-15.96923093125238</v>
       </c>
       <c r="F66">
-        <v>7.601905142323679</v>
+        <v>5.372042811545358</v>
       </c>
       <c r="G66">
-        <v>-8.475272776264918</v>
+        <v>-13.0907079274326</v>
       </c>
     </row>
     <row r="67" spans="1:7">
@@ -1921,13 +1921,13 @@
         <v>-7.300992318469945</v>
       </c>
       <c r="E67">
-        <v>-12.82985726848689</v>
+        <v>-13.50195526680929</v>
       </c>
       <c r="F67">
-        <v>7.448753263424496</v>
+        <v>5.142452502185447</v>
       </c>
       <c r="G67">
-        <v>-8.243113226047965</v>
+        <v>-15.20229704674376</v>
       </c>
     </row>
     <row r="68" spans="1:7">
@@ -1944,13 +1944,13 @@
         <v>-7.230602662364817</v>
       </c>
       <c r="E68">
-        <v>-13.70936390483461</v>
+        <v>-13.94145725467573</v>
       </c>
       <c r="F68">
-        <v>7.33420661896538</v>
+        <v>5.362905919092479</v>
       </c>
       <c r="G68">
-        <v>-8.547679492417183</v>
+        <v>-14.51101421043228</v>
       </c>
     </row>
     <row r="69" spans="1:7">
@@ -1967,13 +1967,13 @@
         <v>-7.158417361434538</v>
       </c>
       <c r="E69">
-        <v>-13.1860398630862</v>
+        <v>-15.79742968434938</v>
       </c>
       <c r="F69">
-        <v>7.128426902231539</v>
+        <v>3.777591294228036</v>
       </c>
       <c r="G69">
-        <v>-8.02462652606922</v>
+        <v>-11.92079494285571</v>
       </c>
     </row>
     <row r="70" spans="1:7">
@@ -1990,13 +1990,13 @@
         <v>-7.088343687113963</v>
       </c>
       <c r="E70">
-        <v>-13.33406209297492</v>
+        <v>-13.28884075153432</v>
       </c>
       <c r="F70">
-        <v>6.919457970996918</v>
+        <v>4.644885338019896</v>
       </c>
       <c r="G70">
-        <v>-7.32842349802936</v>
+        <v>-11.26563015285982</v>
       </c>
     </row>
     <row r="71" spans="1:7">
@@ -2013,13 +2013,13 @@
         <v>-7.022226621147922</v>
       </c>
       <c r="E71">
-        <v>-12.34846689604951</v>
+        <v>-12.89538881585189</v>
       </c>
       <c r="F71">
-        <v>7.184086564760443</v>
+        <v>4.402859577209158</v>
       </c>
       <c r="G71">
-        <v>-7.472462562045864</v>
+        <v>-12.78560025950608</v>
       </c>
     </row>
     <row r="72" spans="1:7">
@@ -2036,13 +2036,13 @@
         <v>-6.964380057859183</v>
       </c>
       <c r="E72">
-        <v>-14.55841655348073</v>
+        <v>-15.17174401613159</v>
       </c>
       <c r="F72">
-        <v>6.570090705396615</v>
+        <v>4.761759694880878</v>
       </c>
       <c r="G72">
-        <v>-6.413592677483697</v>
+        <v>-11.62582624954787</v>
       </c>
     </row>
     <row r="73" spans="1:7">
@@ -2059,13 +2059,13 @@
         <v>-6.916690285639091</v>
       </c>
       <c r="E73">
-        <v>-13.57067485987569</v>
+        <v>-16.54776612810231</v>
       </c>
       <c r="F73">
-        <v>5.891624667807708</v>
+        <v>4.308147361842674</v>
       </c>
       <c r="G73">
-        <v>-6.51219994778813</v>
+        <v>-11.06844514324499</v>
       </c>
     </row>
     <row r="74" spans="1:7">
@@ -2082,13 +2082,13 @@
         <v>-6.881028599590123</v>
       </c>
       <c r="E74">
-        <v>-12.76296717891959</v>
+        <v>-15.09996770311002</v>
       </c>
       <c r="F74">
-        <v>5.887865536533805</v>
+        <v>3.184803297110681</v>
       </c>
       <c r="G74">
-        <v>-4.887844339671261</v>
+        <v>-11.42588829504466</v>
       </c>
     </row>
     <row r="75" spans="1:7">
@@ -2105,13 +2105,13 @@
         <v>-6.856206971784651</v>
       </c>
       <c r="E75">
-        <v>-13.57594600362062</v>
+        <v>-12.90607148603598</v>
       </c>
       <c r="F75">
-        <v>6.187805775943866</v>
+        <v>5.466188423608327</v>
       </c>
       <c r="G75">
-        <v>-6.113531528315597</v>
+        <v>-9.271520249652248</v>
       </c>
     </row>
     <row r="76" spans="1:7">
@@ -2128,13 +2128,13 @@
         <v>-6.846887230876835</v>
       </c>
       <c r="E76">
-        <v>-11.54977087836867</v>
+        <v>-15.31874733936859</v>
       </c>
       <c r="F76">
-        <v>6.061304133127548</v>
+        <v>4.356701288790364</v>
       </c>
       <c r="G76">
-        <v>-5.437517856531</v>
+        <v>-9.875855636470776</v>
       </c>
     </row>
     <row r="77" spans="1:7">
@@ -2151,13 +2151,13 @@
         <v>-6.854257762838099</v>
       </c>
       <c r="E77">
-        <v>-13.58057410405646</v>
+        <v>-16.32105713385631</v>
       </c>
       <c r="F77">
-        <v>6.013177643759702</v>
+        <v>3.870631864175671</v>
       </c>
       <c r="G77">
-        <v>-5.189979220864931</v>
+        <v>-8.95820952782711</v>
       </c>
     </row>
     <row r="78" spans="1:7">
@@ -2174,13 +2174,13 @@
         <v>-6.877027960779938</v>
       </c>
       <c r="E78">
-        <v>-13.89240029575063</v>
+        <v>-16.11785091971011</v>
       </c>
       <c r="F78">
-        <v>5.327859351014838</v>
+        <v>3.514839780999255</v>
       </c>
       <c r="G78">
-        <v>-5.734885122798795</v>
+        <v>-7.269755256546488</v>
       </c>
     </row>
     <row r="79" spans="1:7">
@@ -2197,13 +2197,13 @@
         <v>-6.915845813511584</v>
       </c>
       <c r="E79">
-        <v>-15.32511437382337</v>
+        <v>-15.07437276801866</v>
       </c>
       <c r="F79">
-        <v>5.202747708700417</v>
+        <v>3.518600569007964</v>
       </c>
       <c r="G79">
-        <v>-3.936815082881805</v>
+        <v>-8.949747257425301</v>
       </c>
     </row>
     <row r="80" spans="1:7">
@@ -2220,13 +2220,13 @@
         <v>-6.971723674195574</v>
       </c>
       <c r="E80">
-        <v>-16.20885513336826</v>
+        <v>-18.25380531185601</v>
       </c>
       <c r="F80">
-        <v>4.955658966323769</v>
+        <v>3.470621529037818</v>
       </c>
       <c r="G80">
-        <v>-4.127667334886906</v>
+        <v>-9.047852500831139</v>
       </c>
     </row>
     <row r="81" spans="1:7">
@@ -2243,13 +2243,13 @@
         <v>-7.044944849539955</v>
       </c>
       <c r="E81">
-        <v>-15.41466494732505</v>
+        <v>-16.08717050830815</v>
       </c>
       <c r="F81">
-        <v>5.376136603249993</v>
+        <v>3.716933262790639</v>
       </c>
       <c r="G81">
-        <v>-3.473903626496904</v>
+        <v>-6.958787326914794</v>
       </c>
     </row>
     <row r="82" spans="1:7">
@@ -2266,13 +2266,13 @@
         <v>-7.135516355596254</v>
       </c>
       <c r="E82">
-        <v>-17.37720595582122</v>
+        <v>-19.19849027459612</v>
       </c>
       <c r="F82">
-        <v>4.854922863204127</v>
+        <v>2.812016428298431</v>
       </c>
       <c r="G82">
-        <v>-2.571400355350075</v>
+        <v>-7.68367807504888</v>
       </c>
     </row>
     <row r="83" spans="1:7">
@@ -2289,13 +2289,13 @@
         <v>-7.241222901042937</v>
       </c>
       <c r="E83">
-        <v>-17.15127585910454</v>
+        <v>-17.88394219727953</v>
       </c>
       <c r="F83">
-        <v>4.554790442556616</v>
+        <v>2.942129752990955</v>
       </c>
       <c r="G83">
-        <v>-1.818986720775367</v>
+        <v>-6.756109552409453</v>
       </c>
     </row>
     <row r="84" spans="1:7">
@@ -2312,13 +2312,13 @@
         <v>-7.365438951162127</v>
       </c>
       <c r="E84">
-        <v>-17.46785694850676</v>
+        <v>-17.52173673225003</v>
       </c>
       <c r="F84">
-        <v>4.898983725359033</v>
+        <v>2.707792898413003</v>
       </c>
       <c r="G84">
-        <v>-2.613524677730227</v>
+        <v>-7.735308096286742</v>
       </c>
     </row>
     <row r="85" spans="1:7">
@@ -2335,13 +2335,13 @@
         <v>-7.507305186527121</v>
       </c>
       <c r="E85">
-        <v>-18.14129990360944</v>
+        <v>-20.61340292134471</v>
       </c>
       <c r="F85">
-        <v>4.574598363892358</v>
+        <v>2.399736315190311</v>
       </c>
       <c r="G85">
-        <v>-2.927711485711737</v>
+        <v>-5.100185311669167</v>
       </c>
     </row>
     <row r="86" spans="1:7">
@@ -2358,13 +2358,13 @@
         <v>-7.661240528896315</v>
       </c>
       <c r="E86">
-        <v>-20.4054055816984</v>
+        <v>-20.23044345993805</v>
       </c>
       <c r="F86">
-        <v>4.611005111245396</v>
+        <v>2.571948928027912</v>
       </c>
       <c r="G86">
-        <v>-1.517980579798146</v>
+        <v>-7.089511193843071</v>
       </c>
     </row>
     <row r="87" spans="1:7">
@@ -2381,13 +2381,13 @@
         <v>-7.826983043053469</v>
       </c>
       <c r="E87">
-        <v>-20.56300100563934</v>
+        <v>-21.0188779555175</v>
       </c>
       <c r="F87">
-        <v>5.088525784263199</v>
+        <v>2.41996339043187</v>
       </c>
       <c r="G87">
-        <v>-1.832607071468622</v>
+        <v>-4.856114927191431</v>
       </c>
     </row>
     <row r="88" spans="1:7">
@@ -2404,13 +2404,13 @@
         <v>-8.00280488150999</v>
       </c>
       <c r="E88">
-        <v>-20.83067004728472</v>
+        <v>-24.44396662884894</v>
       </c>
       <c r="F88">
-        <v>3.961074673948126</v>
+        <v>2.091605178901368</v>
       </c>
       <c r="G88">
-        <v>-1.553112619035121</v>
+        <v>-4.857135387096418</v>
       </c>
     </row>
     <row r="89" spans="1:7">
@@ -2427,13 +2427,13 @@
         <v>-8.186876682653661</v>
       </c>
       <c r="E89">
-        <v>-23.28042051731812</v>
+        <v>-23.69730277751624</v>
       </c>
       <c r="F89">
-        <v>4.414880844958585</v>
+        <v>1.813464256063378</v>
       </c>
       <c r="G89">
-        <v>-1.31161799348155</v>
+        <v>-5.459275636691677</v>
       </c>
     </row>
     <row r="90" spans="1:7">
@@ -2450,13 +2450,13 @@
         <v>-8.376793544761238</v>
       </c>
       <c r="E90">
-        <v>-25.8132232006522</v>
+        <v>-26.10128396075412</v>
       </c>
       <c r="F90">
-        <v>4.038565131010409</v>
+        <v>0.7641812073460782</v>
       </c>
       <c r="G90">
-        <v>-1.473221436505761</v>
+        <v>-2.051146270992318</v>
       </c>
     </row>
     <row r="91" spans="1:7">
@@ -2473,13 +2473,13 @@
         <v>-8.571277486618841</v>
       </c>
       <c r="E91">
-        <v>-26.29730348665013</v>
+        <v>-25.20758508686636</v>
       </c>
       <c r="F91">
-        <v>3.056523977847956</v>
+        <v>2.03836766265825</v>
       </c>
       <c r="G91">
-        <v>-0.7473069472451284</v>
+        <v>-1.688935504266776</v>
       </c>
     </row>
     <row r="92" spans="1:7">
@@ -2496,13 +2496,13 @@
         <v>-8.771999332443656</v>
       </c>
       <c r="E92">
-        <v>-29.64813424320379</v>
+        <v>-26.64408496920952</v>
       </c>
       <c r="F92">
-        <v>3.119832784974311</v>
+        <v>1.256879227917974</v>
       </c>
       <c r="G92">
-        <v>-0.07635948154831343</v>
+        <v>-3.951829952737824</v>
       </c>
     </row>
     <row r="93" spans="1:7">
@@ -2519,13 +2519,13 @@
         <v>-8.978787589855461</v>
       </c>
       <c r="E93">
-        <v>-28.42934074877939</v>
+        <v>-28.60830151308852</v>
       </c>
       <c r="F93">
-        <v>3.281770328547586</v>
+        <v>0.5743715857708078</v>
       </c>
       <c r="G93">
-        <v>0.4514479748392852</v>
+        <v>-4.34534029191891</v>
       </c>
     </row>
     <row r="94" spans="1:7">
@@ -2542,13 +2542,13 @@
         <v>-9.186692292658304</v>
       </c>
       <c r="E94">
-        <v>-31.28895660853603</v>
+        <v>-31.58132847589325</v>
       </c>
       <c r="F94">
-        <v>2.68646078105611</v>
+        <v>0.7895590710982439</v>
       </c>
       <c r="G94">
-        <v>-0.7009596927179718</v>
+        <v>-5.024599091825798</v>
       </c>
     </row>
     <row r="95" spans="1:7">
@@ -2565,13 +2565,13 @@
         <v>-9.398898639385123</v>
       </c>
       <c r="E95">
-        <v>-31.63216059662935</v>
+        <v>-35.15543337915809</v>
       </c>
       <c r="F95">
-        <v>2.164610854844895</v>
+        <v>-0.8509662411627866</v>
       </c>
       <c r="G95">
-        <v>-1.029373877381234</v>
+        <v>-4.23915668103372</v>
       </c>
     </row>
     <row r="96" spans="1:7">
@@ -2588,13 +2588,13 @@
         <v>-9.615079859928903</v>
       </c>
       <c r="E96">
-        <v>-34.83959043101911</v>
+        <v>-34.18852719446234</v>
       </c>
       <c r="F96">
-        <v>2.165054859772795</v>
+        <v>-0.0555430099726174</v>
       </c>
       <c r="G96">
-        <v>0.5152841402782822</v>
+        <v>-5.480675763702376</v>
       </c>
     </row>
     <row r="97" spans="1:7">
@@ -2611,13 +2611,13 @@
         <v>-9.832979548077496</v>
       </c>
       <c r="E97">
-        <v>-36.93511460722453</v>
+        <v>-37.13172509897854</v>
       </c>
       <c r="F97">
-        <v>1.352403243339201</v>
+        <v>-0.4193396073622847</v>
       </c>
       <c r="G97">
-        <v>0.862827846633107</v>
+        <v>-4.455267776603427</v>
       </c>
     </row>
     <row r="98" spans="1:7">
@@ -2634,13 +2634,13 @@
         <v>-10.04930259755516</v>
       </c>
       <c r="E98">
-        <v>-39.86623054308827</v>
+        <v>-37.86059657593511</v>
       </c>
       <c r="F98">
-        <v>1.464522771308115</v>
+        <v>-0.9269656369000301</v>
       </c>
       <c r="G98">
-        <v>-0.192416288105873</v>
+        <v>-6.237932481298825</v>
       </c>
     </row>
     <row r="99" spans="1:7">
@@ -2657,13 +2657,13 @@
         <v>-10.25858950227421</v>
       </c>
       <c r="E99">
-        <v>-41.67587894790046</v>
+        <v>-39.95663020546639</v>
       </c>
       <c r="F99">
-        <v>0.7418384817577699</v>
+        <v>-0.3016426816703225</v>
       </c>
       <c r="G99">
-        <v>-0.1160655436391539</v>
+        <v>-3.321402292078592</v>
       </c>
     </row>
     <row r="100" spans="1:7">
@@ -2680,13 +2680,13 @@
         <v>-10.45844756998324</v>
       </c>
       <c r="E100">
-        <v>-44.44884472175733</v>
+        <v>-45.6196839406775</v>
       </c>
       <c r="F100">
-        <v>0.7441811047728869</v>
+        <v>-1.117626820165378</v>
       </c>
       <c r="G100">
-        <v>-0.5493147571266748</v>
+        <v>-4.81588058842952</v>
       </c>
     </row>
     <row r="101" spans="1:7">
@@ -2703,13 +2703,13 @@
         <v>-10.63576900685155</v>
       </c>
       <c r="E101">
-        <v>-47.12933452790356</v>
+        <v>-46.84625056073607</v>
       </c>
       <c r="F101">
-        <v>0.6460477320328407</v>
+        <v>-0.8005658832742564</v>
       </c>
       <c r="G101">
-        <v>-1.783497028388413</v>
+        <v>-6.890140890669651</v>
       </c>
     </row>
     <row r="102" spans="1:7">
@@ -2726,13 +2726,13 @@
         <v>-10.78442059877011</v>
       </c>
       <c r="E102">
-        <v>-47.98810075329614</v>
+        <v>-46.93459882438871</v>
       </c>
       <c r="F102">
-        <v>0.6021715958087592</v>
+        <v>-2.549732408779845</v>
       </c>
       <c r="G102">
-        <v>-1.88650769802562</v>
+        <v>-6.693566188264877</v>
       </c>
     </row>
   </sheetData>
